--- a/data/trans_orig/P1806_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301968</t>
+          <t>302340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310555</t>
+          <t>310682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285056</t>
+          <t>285389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288972</t>
+          <t>289019</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>590004</t>
+          <t>589726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598921</t>
+          <t>598850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>25024</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45351</t>
+          <t>45946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>501024</t>
+          <t>500253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514352</t>
+          <t>514784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479819</t>
+          <t>479167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495743</t>
+          <t>496581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>986764</t>
+          <t>986169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1009070</t>
+          <t>1007091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42098</t>
+          <t>42065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>34109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>55280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297936</t>
+          <t>297946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309484</t>
+          <t>309818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307030</t>
+          <t>307063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323846</t>
+          <t>323681</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>608751</t>
+          <t>609898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>630228</t>
+          <t>631069</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30694</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>43109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293077</t>
+          <t>293049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306955</t>
+          <t>307299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445024</t>
+          <t>444746</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463422</t>
+          <t>463564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>744129</t>
+          <t>745165</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766881</t>
+          <t>766650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7478</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170940</t>
+          <t>171118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177104</t>
+          <t>177072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197155</t>
+          <t>197436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204066</t>
+          <t>203884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371030</t>
+          <t>370961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379833</t>
+          <t>379920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18701</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22550</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250935</t>
+          <t>250177</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265318</t>
+          <t>264866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234506</t>
+          <t>235818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247120</t>
+          <t>247436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493393</t>
+          <t>493541</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510143</t>
+          <t>510639</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42834</t>
+          <t>42397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28805</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86364</t>
+          <t>87658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112614</t>
+          <t>114355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>581445</t>
+          <t>581882</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605585</t>
+          <t>606862</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>762901</t>
+          <t>761607</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>820460</t>
+          <t>819095</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1360930</t>
+          <t>1359189</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1416554</t>
+          <t>1416995</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>22844</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29518</t>
+          <t>30779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>915830</t>
+          <t>916235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>926777</t>
+          <t>926979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>695868</t>
+          <t>694887</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>708132</t>
+          <t>707473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1616934</t>
+          <t>1615673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1635639</t>
+          <t>1634458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>58876</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>102574</t>
+          <t>98977</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>145653</t>
+          <t>144518</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205827</t>
+          <t>207013</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>223998</t>
+          <t>223470</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295999</t>
+          <t>293469</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3357243</t>
+          <t>3360840</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3399660</t>
+          <t>3400941</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3455086</t>
+          <t>3453900</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3515260</t>
+          <t>3516395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6824731</t>
+          <t>6827261</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6896732</t>
+          <t>6897260</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1806_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>308129</t>
+          <t>315322</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302340</t>
+          <t>310874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310682</t>
+          <t>317829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>287801</t>
+          <t>313627</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285389</t>
+          <t>310627</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289019</t>
+          <t>315094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>595928</t>
+          <t>628949</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>589726</t>
+          <t>623868</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598850</t>
+          <t>632151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34558</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33391</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25024</t>
+          <t>24606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>46923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>509484</t>
+          <t>521739</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500253</t>
+          <t>513490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514784</t>
+          <t>526692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>489240</t>
+          <t>520334</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479167</t>
+          <t>510600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496581</t>
+          <t>528432</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>998724</t>
+          <t>1042073</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>986169</t>
+          <t>1028937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1007091</t>
+          <t>1051254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032115</t>
+          <t>1075860</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33132</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25447</t>
+          <t>26649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>43471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>44330</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>34886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55280</t>
+          <t>55164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>305250</t>
+          <t>305389</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297946</t>
+          <t>298254</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>309818</t>
+          <t>309957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>315996</t>
+          <t>322655</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307063</t>
+          <t>312910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323681</t>
+          <t>329732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>621246</t>
+          <t>628045</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609898</t>
+          <t>617211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>631069</t>
+          <t>637489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21377</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30972</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31292</t>
+          <t>33644</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21624</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43109</t>
+          <t>45411</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>302642</t>
+          <t>362974</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293049</t>
+          <t>351618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307299</t>
+          <t>367657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>454341</t>
+          <t>398488</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444746</t>
+          <t>391031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463564</t>
+          <t>405004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>756982</t>
+          <t>761463</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745165</t>
+          <t>749696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766650</t>
+          <t>770091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>174747</t>
+          <t>201421</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171118</t>
+          <t>196943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177072</t>
+          <t>203896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>201235</t>
+          <t>219436</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197436</t>
+          <t>215242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203884</t>
+          <t>222464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>375982</t>
+          <t>420856</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370961</t>
+          <t>415487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379920</t>
+          <t>424796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33151</t>
+          <t>32689</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>260662</t>
+          <t>262558</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250177</t>
+          <t>254961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264866</t>
+          <t>266491</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>242716</t>
+          <t>249213</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235818</t>
+          <t>241765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247436</t>
+          <t>253943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>503378</t>
+          <t>511771</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493541</t>
+          <t>501768</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510639</t>
+          <t>518650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>44296</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61714</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>56380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87658</t>
+          <t>87841</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>89509</t>
+          <t>100211</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56549</t>
+          <t>82332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114355</t>
+          <t>122941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>596484</t>
+          <t>689942</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>581882</t>
+          <t>675391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>606862</t>
+          <t>700242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>787551</t>
+          <t>701591</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761607</t>
+          <t>684216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>819095</t>
+          <t>715677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1384035</t>
+          <t>1391533</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1359189</t>
+          <t>1368803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1416995</t>
+          <t>1409412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30779</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>922792</t>
+          <t>791474</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>916235</t>
+          <t>784830</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>926979</t>
+          <t>795060</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>702638</t>
+          <t>814488</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694887</t>
+          <t>807183</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>707473</t>
+          <t>820748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1625431</t>
+          <t>1605962</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1615673</t>
+          <t>1596573</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1634458</t>
+          <t>1613486</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>79627</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58876</t>
+          <t>65067</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>98977</t>
+          <t>102269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>179396</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>144518</t>
+          <t>171546</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207013</t>
+          <t>218572</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>259023</t>
+          <t>276079</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>223470</t>
+          <t>246892</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>293469</t>
+          <t>304186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3380190</t>
+          <t>3450820</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3360840</t>
+          <t>3430493</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3400941</t>
+          <t>3467695</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3481517</t>
+          <t>3539833</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3453900</t>
+          <t>3515398</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3516395</t>
+          <t>3562424</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6861707</t>
+          <t>6990653</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6827261</t>
+          <t>6962546</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6897260</t>
+          <t>7019840</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
